--- a/artfynd/A 48219-2023 artfynd.xlsx
+++ b/artfynd/A 48219-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117455550</v>
+        <v>117455530</v>
       </c>
       <c r="B2" t="n">
-        <v>91064</v>
+        <v>79561</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446518</v>
+        <v>446195</v>
       </c>
       <c r="R2" t="n">
-        <v>7055241</v>
+        <v>7055248</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117455530</v>
+        <v>117455550</v>
       </c>
       <c r="B3" t="n">
-        <v>79561</v>
+        <v>91064</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446195</v>
+        <v>446518</v>
       </c>
       <c r="R3" t="n">
-        <v>7055248</v>
+        <v>7055241</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117721354</v>
+        <v>117721356</v>
       </c>
       <c r="B5" t="n">
-        <v>77417</v>
+        <v>74592</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117721356</v>
+        <v>117724681</v>
       </c>
       <c r="B6" t="n">
-        <v>74592</v>
+        <v>74597</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långnäsudden (Långnäsudden), Jmt</t>
+          <t>Bodberget (Bodberget), Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446427</v>
+        <v>446171</v>
       </c>
       <c r="R6" t="n">
-        <v>7055266</v>
+        <v>7055005</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117724681</v>
+        <v>117721354</v>
       </c>
       <c r="B7" t="n">
-        <v>74597</v>
+        <v>77417</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bodberget (Bodberget), Jmt</t>
+          <t>Långnäsudden (Långnäsudden), Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446171</v>
+        <v>446427</v>
       </c>
       <c r="R7" t="n">
-        <v>7055005</v>
+        <v>7055266</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 48219-2023 artfynd.xlsx
+++ b/artfynd/A 48219-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117455530</v>
       </c>
       <c r="B2" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117455550</v>
+        <v>117455551</v>
       </c>
       <c r="B3" t="n">
-        <v>91064</v>
+        <v>86818</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446518</v>
+        <v>446479</v>
       </c>
       <c r="R3" t="n">
-        <v>7055241</v>
+        <v>7055257</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117455551</v>
+        <v>117455550</v>
       </c>
       <c r="B4" t="n">
-        <v>86816</v>
+        <v>91066</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446479</v>
+        <v>446518</v>
       </c>
       <c r="R4" t="n">
-        <v>7055257</v>
+        <v>7055241</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>117721356</v>
       </c>
       <c r="B5" t="n">
-        <v>74592</v>
+        <v>74594</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>117724681</v>
       </c>
       <c r="B6" t="n">
-        <v>74597</v>
+        <v>74599</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>117721354</v>
       </c>
       <c r="B7" t="n">
-        <v>77417</v>
+        <v>77419</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
